--- a/TESTS/zlit_6_hohol.xlsx
+++ b/TESTS/zlit_6_hohol.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Микола Гоголь — видатний письменник що народився на Полтавщині і писав переважно російською</t>
+          <t>Микола Гоголь</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>До «Вечорів на хуторі біля Диканьки» — циклу повістей про українське народне життя і фольклор</t>
+          <t>До «Вечорів на хуторі біля Диканьки»</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>У селі Диканька на Полтавщині у різдвяну ніч — поєднання реального і фантастичного</t>
+          <t>У селі Диканька на Полтавщині у різдвяну ніч</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Вакула — молодий коваль талановитий і закоханий у красуню Оксану</t>
+          <t>Вакула</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Принести їй черевички самої царіці — вона думала що це нездійсненна вимога</t>
+          <t>Принести їй черевички самої царіці</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Вона кокетлива і примхлива — хотіла похвалитись перед подругами і не вірила що Вакула здатен на це</t>
+          <t>Вона кокетлива і примхлива</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Мати Вакули — відьма що дружить з чортом і морочить голову місцевим чоловікам</t>
+          <t>Мати Вакули</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Краде місяць щоб Чуб не пішов до дяка і Вакула не зміг виконати бажання Оксани — чорт мстить за карикатуру</t>
+          <t>Краде місяць щоб Чуб не пішов до дяка і Вакула не зміг виконати бажання Оксани</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -916,7 +961,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>За намальовану карикатуру де чорт зображений у принизливому вигляді — Вакула хороший маляр</t>
+          <t>За намальовану карикатуру де чорт зображений у принизливому вигляді</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -937,6 +982,11 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Хто такий Пацюк, до якого звернувся Вакула за допомогою?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Священник</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Місцевий знахар, про якого казали, що він знається з нечистою силою</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сусід-кравець</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лікар</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Що дивовижне побачив Вакула, коли прийшов до Пацюка?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пацюк спав</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Галушки самі підстрибували, занурювались у сметану і летіли йому до рота</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пацюк готував зілля</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У хаті нікого не було</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому Вакула злякався і втік від Пацюка, перехрестившись?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пацюк прогнав його</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він зрозумів, що поруч сидить чорт, і перехрестився — після чого чорт опинився в нього на спині</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пацюк на нього накричав</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Почув грім</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Чому Чуб (батько Оксани) вирушив того вечора з дому, попри хуртовину?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>В гості до Солохи, не підозрюючи нічого</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дяк переконав його, що варто піти випити й погуляти</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>За дровами</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>До церкви</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Що сталося з Чубом і дяком у завірюсі, коли чорт украв місяць і стало темно?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони дійшли спокійно</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Збилися з дороги в темряві, хоч ішли біля власних домівок</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Зустріли Вакулу</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Повернулись одразу</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що сталося з Чубом, коли він зрештою дістався хати, де гостювала Солоха?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Його гостинно прийняли</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вакула в темряві не впізнав його і прогнав геть, прийнявши за чужого</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він заснув на порозі</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Його впізнала Солоха</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Скількох поважних гостей того вечора приймала вдома Солоха?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одного</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Кількох — голову, дяка та інших, що приходили по черзі, не знаючи один про одного</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Нікого</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Усе село</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що Солоха робила, коли один гість стукав у двері, а інший уже сидів у хаті?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Виганяла обох</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Ховала того, хто вже був у хаті, у великий мішок, що стояв у кутку</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Тікала сама</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гасила свічку й тікала</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Що зробив Вакула, прийшовши додому й побачивши мішки в хаті?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Залишив усе як є</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Не знаючи, хто в мішках, виніс їх із хати, як непотрібні речі</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розв'язав усі мішки одразу</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Спалив мішки</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Як чорт опинився верхи на Вакулі, коли той вийшов з хати Пацюка?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вакула сам покликав чорта</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чорт, переляканий Вакулою, перекинувся і вистрибнув йому на спину</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Чорт прилетів з неба</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Чорт чекав на вулиці</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Що Вакула зробив, відчувши на спині чорта?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Розгубився і втік</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Швидко перехрестив його і міцно вхопив за хвіст, не відпускаючи</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Не помітив його</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Покликав на допомогу</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чого Вакула зажадав від чорта замість того, щоб відпустити його?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Грошей</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Допомогти здобути черевички цариці, погрожуючи інакше провчити його хрестом</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вибачень</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не зажадав</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Що сталося, коли Вакула верхи на чорті здійнявся у повітря?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Чорт одразу скинув його</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони полетіли понад хмарами, минаючи зорі, швидко наближаючись до Петербурга</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони полетіли в інший бік</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Чорт зник у повітрі</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Кого Вакула побачив у повітрі під час польоту до Петербурга?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ангелів</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Відьму на мітлі, що теж летіла кудись уночі</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Інших чортів</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Птахів</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як Вакула почувався, опинившись уперше в незнайомому Петербурзі?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Спокійно, як удома</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Враженим і трохи розгубленим серед розкішних будівель і незнайомого натовпу</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Байдуже</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Розгніваним</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>З ким Вакула опинився поруч у Петербурзі, що допомогло йому потрапити до палацу?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сам по собі</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З запорізькими козаками, що прибули до цариці з проханням</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>З купцями</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>З солдатами</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Про що козаки просили (клопотали) перед царицею, поки там був Вакула?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Про гроші</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Про збереження своїх прав і вольностей</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Про звільнення в'язнів</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Про дозвіл на торгівлю</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як цариця поставилась до простого сільського коваля Вакули серед своїх придворних?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Прогнала його</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З цікавістю і доброзичливо вислухала його прохання й подарувала йому власні черевички</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розгнівалась</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не помітила його</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Що Оксана дізналась, поки Вакула вночі був відсутній?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого особливого</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Чутки, що Вакула, можливо, втопився з горя через неї, через що вона відчула докори сумління</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що Вакула одружився</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що Вакула втік з села</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Як Оксана почувалась, коли вранці побачила Вакулу живим, з черевичками цариці?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Байдуже</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зрозуміла, що любить його ще до того, як побачила черевички — вони вже були не такі важливі</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Розгнівалась</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не впізнала його</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чим закінчується повість «Ніч перед Різдвом»?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сумно — Вакула і Оксана розлучаються</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Весело — Вакула й Оксана одружуються, а чорт залишається покараним</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Чорт мстить знову</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічим не закінчується</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Який жанр «Ночі перед Різдвом»?</t>
+          <t>«Ніч перед Різдвом» поєднує реалістичні картини сільського побуту з фантастичними і комічними елементами.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,29 +2133,32 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграють фантастичні елементи у повісті Гоголя?</t>
+          <t>Фантастичні елементи (чорт, відьма) у повісті використані лише для того, щоб налякати читача.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,21 +2170,19 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що особливого в тому що Вакула приборкав чорта?</t>
+          <t>Те, що Вакула перехрестив і приборкав чорта, підкреслює перевагу людської віри й сміливості над нечистою силою.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>А</t>
@@ -2023,6 +2191,11 @@
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Чим закінчується «Ніч перед Різдвом»?</t>
+          <t>Повість «Ніч перед Різдвом» закінчується весільним святкуванням Вакули і Оксани.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Яка трансформація відбувається з Оксаною наприкінці?</t>
+          <t>Оксана поставила Вакулі умову принести черевички, бажаючи назавжди прогнати його від себе.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Ночі перед Різдвом»?</t>
+          <t>Головна ідея повісті — кохання й людська гідність можуть подолати навіть нечисту силу та примхи.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які фантастичні елементи є у «Ночі перед Різдвом»?</t>
+          <t>Що відбувається у повісті «Ніч перед Різдвом»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>Вакула летить до Петербурга на чорті</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>Чорт краде місяць</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Відьма Солоха літає на мітлі</t>
-        </is>
-      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Говорячий кіт</t>
+          <t>Оксана назавжди прогнала Вакулу</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Вакула летить на чорті до Петербурга</t>
+          <t>Вакула отримує черевички цариці</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Схопив чорта і верхи на ньому полетів до Петербурга — використав нечисту силу собі на службу</t>
+          <t>Схопив чорта і верхи на ньому полетів до Петербурга</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Він вразив усіх своєю щирістю простотою і сміливістю — цариця була зачарована його народністю</t>
+          <t>Він вразив усіх своєю щирістю простотою і сміливістю</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
